--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kajih\Desktop\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kajih\Desktop\temp\git_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEA62D68-9CA4-4CA2-8B32-E62BF5C2AB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6996E833-A06C-4C03-9F6F-8552E1F96ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7365" yWindow="2310" windowWidth="27255" windowHeight="18315" activeTab="1" xr2:uid="{2C4B1875-BA31-4357-A622-0665D8DE9F73}"/>
+    <workbookView xWindow="7365" yWindow="2310" windowWidth="27255" windowHeight="18315" xr2:uid="{2C4B1875-BA31-4357-A622-0665D8DE9F73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,15 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>up1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,8 +406,8 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kajih\Desktop\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kajih\Desktop\temp\git_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEA62D68-9CA4-4CA2-8B32-E62BF5C2AB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7398AD0-BDDC-41BC-9CF7-424489DE9A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7365" yWindow="2310" windowWidth="27255" windowHeight="18315" activeTab="1" xr2:uid="{2C4B1875-BA31-4357-A622-0665D8DE9F73}"/>
   </bookViews>
@@ -32,6 +32,15 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>up2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,8 +422,8 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1">
-        <v>2</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kajih\Desktop\temp\git_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75545974-DA4D-4BE7-82CF-B119D391235D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EC0BA0-BD6C-4314-AA0B-223F6C2ED179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7365" yWindow="2310" windowWidth="27255" windowHeight="18315" activeTab="1" xr2:uid="{2C4B1875-BA31-4357-A622-0665D8DE9F73}"/>
+    <workbookView xWindow="7365" yWindow="2310" windowWidth="27255" windowHeight="18315" activeTab="2" xr2:uid="{2C4B1875-BA31-4357-A622-0665D8DE9F73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,13 +36,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>up1</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>up2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sin1</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -434,4 +439,20 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5679523C-037E-492A-BA7A-D05830D504A9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kajih\Desktop\temp\git_learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75545974-DA4D-4BE7-82CF-B119D391235D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9929D2F-6552-4A7A-91E3-92B1EE4D8360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7365" yWindow="2310" windowWidth="27255" windowHeight="18315" activeTab="1" xr2:uid="{2C4B1875-BA31-4357-A622-0665D8DE9F73}"/>
   </bookViews>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11181DF7-BDED-4C53-BBBA-2B6A0DDB330C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -430,6 +430,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
